--- a/artfynd/A 59876-2025 artfynd.xlsx
+++ b/artfynd/A 59876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130722726</v>
       </c>
       <c r="B2" t="n">
-        <v>58011</v>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>130722722</v>
       </c>
       <c r="B3" t="n">
-        <v>57791</v>
+        <v>57799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59876-2025 artfynd.xlsx
+++ b/artfynd/A 59876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130722726</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>130722722</v>
       </c>
       <c r="B3" t="n">
-        <v>57799</v>
+        <v>57800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59876-2025 artfynd.xlsx
+++ b/artfynd/A 59876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130722726</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>130722722</v>
       </c>
       <c r="B3" t="n">
-        <v>57800</v>
+        <v>57801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59876-2025 artfynd.xlsx
+++ b/artfynd/A 59876-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130722726</v>
+        <v>130722722</v>
       </c>
       <c r="B2" t="n">
-        <v>58041</v>
+        <v>57890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100082</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -705,16 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -768,11 +764,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Varnande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130722722</v>
+        <v>130722726</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,12 +820,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -888,6 +883,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Varnande</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 59876-2025 artfynd.xlsx
+++ b/artfynd/A 59876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130722722</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130722726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>